--- a/database/Vlr_ObjetivoClie.xlsx
+++ b/database/Vlr_ObjetivoClie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeto_Varejao\bi_flask_app\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CD9679-6DC7-4D8A-B17C-6E1C32DD9E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376AEC40-7CE2-4A1C-8239-C18FD4EC4813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{202ED037-72A0-49D0-AF71-93A226007BD1}"/>
   </bookViews>
@@ -16878,7 +16878,7 @@
         <v>408</v>
       </c>
       <c r="C413" s="2">
-        <v>100</v>
+        <v>20976</v>
       </c>
       <c r="D413" s="1">
         <v>42</v>
